--- a/results/04_final_refined_daily_hydroclimate_data/203/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Max_Temperature_timeseries.xlsx
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>34.8</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -484,7 +484,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>31.4</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -596,7 +596,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>25.1</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -652,7 +652,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>33</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -820,7 +820,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>28.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -946,7 +946,7 @@
         <v>8</v>
       </c>
       <c r="D40">
-        <v>29</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -960,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -974,7 +974,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>32.4</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1058,7 +1058,7 @@
         <v>16</v>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1086,7 +1086,7 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>37</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1100,7 +1100,7 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>33.8</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1114,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="53" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Max_Temperature_timeseries.xlsx
@@ -414,7 +414,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -455,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>34.7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>31.8</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>26.2</v>
+      <c r="D18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -652,7 +652,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -666,7 +666,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -834,7 +834,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="33" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Max_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Max_Temperature_timeseries.xlsx
@@ -498,7 +498,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
